--- a/outputs/protocol_summary.xlsx
+++ b/outputs/protocol_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2769,6 +2769,1944 @@
         </is>
       </c>
       <c r="T23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2165</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>7h 24m</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23.4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2496</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>7h 5m</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Home &amp; A</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>YM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2875</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>5h 51m</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Home &amp; Workshop</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>6h 30m</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Home &amp; Workshop</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>39.6</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>25.8</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>72.1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>7h 21m</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>25.8</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>72.6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>26.6</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>39.7</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/outputs/protocol_summary.xlsx
+++ b/outputs/protocol_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3133,22 +3133,22 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>136</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>71</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>194</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3235,22 +3235,22 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>97</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>133</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>91</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3389,27 +3389,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3439,22 +3439,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>230</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3491,27 +3491,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3541,22 +3541,22 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>153</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>231</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>7h 21m</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3593,27 +3593,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3643,22 +3643,22 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>7h 21m</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3695,27 +3695,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3745,22 +3745,22 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3797,27 +3797,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3847,22 +3847,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>80</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3899,32 +3899,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>50</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4001,97 +4001,97 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>26.6</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2392</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
           <t>25.7</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>25.6</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -4103,32 +4103,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4153,22 +4153,22 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>96</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -4205,22 +4205,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -4307,32 +4307,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4357,22 +4357,22 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>228</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4409,27 +4409,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4459,22 +4459,22 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>117</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>126</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4511,27 +4511,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4561,22 +4561,22 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>131</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>85</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>362</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4613,100 +4613,202 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>25.4</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>51.4</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>39.3</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>2300</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2321</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/outputs/protocol_summary.xlsx
+++ b/outputs/protocol_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4809,6 +4809,1128 @@
         </is>
       </c>
       <c r="T43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>40.1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2507</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2477</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>51.2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>39.2</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>3574</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>72.4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>25.8</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>52.2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>39.7</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>73.9</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>26.9</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2558</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>72.1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>23.3</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>39.8</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2574</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/outputs/protocol_summary.xlsx
+++ b/outputs/protocol_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T54"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5931,6 +5931,1536 @@
         </is>
       </c>
       <c r="T54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>51.2</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>39.2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2505</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2758</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>25.8</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>26.9</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>28.5</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>39.2</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>3292</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>74.4</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>26.6</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>26.3</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>50.6</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2930</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/outputs/protocol_summary.xlsx
+++ b/outputs/protocol_summary.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,106 +413,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>weight_kg</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>bodyfat_pct</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>water_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>muscle_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>bones_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>target_calories</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>target_protein_g</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>target_fat_g</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>target_carbs_g</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>actual_calories</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>actual_protein_g</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>actual_fat_g</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>actual_carbs_g</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>abdgirth_cm</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>steps</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>bmi</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>training</t>
         </is>
@@ -7461,6 +7449,2964 @@
         </is>
       </c>
       <c r="T69" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>26.3</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>28.2</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>74.1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>26.3</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>38.4</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>26.6</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>26.6</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>26.6</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>26.6</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>28.7</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>49.6</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2635</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>27.8</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>3010</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>3033</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>26.9</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>39.9</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>26.9</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>26.9</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>38.5</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2287</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>37.9</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2524</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2554</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>26.9</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>49.6</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>38.3</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>28.5</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>23.3</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>37.9</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>28.2</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
         <is>
           <t>None</t>
         </is>
